--- a/Tools/Luban/DataTables/Datas/__enums__.xlsx
+++ b/Tools/Luban/DataTables/Datas/__enums__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1_Game_Data\Unity\2025TTGJ\Tools\Luban\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB9A83B0-B54F-440A-A2F2-FD791E449487}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3021A8E-5AF8-4379-9372-F5E5904441B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4690" yWindow="3070" windowWidth="30180" windowHeight="16720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15820" yWindow="7850" windowWidth="18780" windowHeight="12970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="67">
   <si>
     <t>##var</t>
   </si>
@@ -185,6 +185,102 @@
   </si>
   <si>
     <t>基础物品</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>if_door</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>if_pumpkin</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>if_hide</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>是否可以举起</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>是否可以被门吞</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>是否可以被南瓜吞</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>是否为隐藏物品</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>lift_true</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>door_false</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>door_true</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>lift_false</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>pumpkin_true</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>pumpkin_false</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>hide_true</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>hide_false</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>可以举起</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>不可以举起</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>可以被门吞</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>不可以被门吞</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>可以被南瓜吞</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>不可以南瓜吞</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>是隐藏物品</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>不是隐藏物品</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>lift</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -523,7 +619,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:L20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
@@ -773,6 +869,166 @@
         <v>42</v>
       </c>
     </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B13" t="s">
+        <v>66</v>
+      </c>
+      <c r="C13" t="b">
+        <v>0</v>
+      </c>
+      <c r="D13" t="b">
+        <v>1</v>
+      </c>
+      <c r="F13" t="s">
+        <v>46</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I13" s="1">
+        <v>0</v>
+      </c>
+      <c r="J13" s="1">
+        <v>0</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H14" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="I14">
+        <v>1</v>
+      </c>
+      <c r="J14">
+        <v>1</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B15" t="s">
+        <v>43</v>
+      </c>
+      <c r="C15" t="b">
+        <v>0</v>
+      </c>
+      <c r="D15" t="b">
+        <v>1</v>
+      </c>
+      <c r="F15" t="s">
+        <v>47</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I15" s="1">
+        <v>0</v>
+      </c>
+      <c r="J15" s="1">
+        <v>0</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H16" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="I16">
+        <v>1</v>
+      </c>
+      <c r="J16">
+        <v>1</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="17" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B17" t="s">
+        <v>44</v>
+      </c>
+      <c r="C17" t="b">
+        <v>0</v>
+      </c>
+      <c r="D17" t="b">
+        <v>1</v>
+      </c>
+      <c r="F17" t="s">
+        <v>48</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="I17" s="1">
+        <v>0</v>
+      </c>
+      <c r="J17" s="1">
+        <v>0</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="18" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="H18" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="I18">
+        <v>1</v>
+      </c>
+      <c r="J18">
+        <v>1</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="19" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B19" t="s">
+        <v>45</v>
+      </c>
+      <c r="C19" t="b">
+        <v>0</v>
+      </c>
+      <c r="D19" t="b">
+        <v>1</v>
+      </c>
+      <c r="F19" t="s">
+        <v>49</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I19" s="1">
+        <v>0</v>
+      </c>
+      <c r="J19" s="1">
+        <v>0</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="20" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="H20" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I20">
+        <v>1</v>
+      </c>
+      <c r="J20">
+        <v>1</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>

--- a/Tools/Luban/DataTables/Datas/__enums__.xlsx
+++ b/Tools/Luban/DataTables/Datas/__enums__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1_Game_Data\Unity\2025TTGJ\Tools\Luban\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3021A8E-5AF8-4379-9372-F5E5904441B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB61493E-058B-4198-9789-60755CD2E9A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15820" yWindow="7850" windowWidth="18780" windowHeight="12970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17330" yWindow="6140" windowWidth="18780" windowHeight="12970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="74">
   <si>
     <t>##var</t>
   </si>
@@ -281,6 +281,34 @@
   </si>
   <si>
     <t>lift</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>特殊</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>房子</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>npc</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>幼苗</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>special</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>house</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>seeding</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -619,7 +647,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L20"/>
+  <dimension ref="A1:L24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
@@ -870,88 +898,64 @@
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B13" t="s">
-        <v>66</v>
-      </c>
-      <c r="C13" t="b">
-        <v>0</v>
-      </c>
-      <c r="D13" t="b">
-        <v>1</v>
-      </c>
-      <c r="F13" t="s">
-        <v>46</v>
-      </c>
       <c r="H13" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="I13" s="1">
-        <v>0</v>
-      </c>
-      <c r="J13" s="1">
-        <v>0</v>
+        <v>71</v>
+      </c>
+      <c r="I13">
+        <v>5</v>
+      </c>
+      <c r="J13">
+        <v>5</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H14" s="1" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="I14">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J14">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B15" t="s">
-        <v>43</v>
-      </c>
-      <c r="C15" t="b">
-        <v>0</v>
-      </c>
-      <c r="D15" t="b">
-        <v>1</v>
-      </c>
-      <c r="F15" t="s">
-        <v>47</v>
-      </c>
       <c r="H15" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="I15" s="1">
-        <v>0</v>
-      </c>
-      <c r="J15" s="1">
-        <v>0</v>
+        <v>69</v>
+      </c>
+      <c r="I15">
+        <v>7</v>
+      </c>
+      <c r="J15">
+        <v>7</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H16" s="1" t="s">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="I16">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J16">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="C17" t="b">
         <v>0</v>
@@ -960,10 +964,10 @@
         <v>1</v>
       </c>
       <c r="F17" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="I17" s="1">
         <v>0</v>
@@ -972,12 +976,12 @@
         <v>0</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.3">
       <c r="H18" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="I18">
         <v>1</v>
@@ -986,12 +990,12 @@
         <v>1</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C19" t="b">
         <v>0</v>
@@ -1000,10 +1004,10 @@
         <v>1</v>
       </c>
       <c r="F19" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I19" s="1">
         <v>0</v>
@@ -1012,20 +1016,100 @@
         <v>0</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="20" spans="2:11" x14ac:dyDescent="0.3">
       <c r="H20" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="I20">
+        <v>1</v>
+      </c>
+      <c r="J20">
+        <v>1</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="21" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B21" t="s">
+        <v>44</v>
+      </c>
+      <c r="C21" t="b">
+        <v>0</v>
+      </c>
+      <c r="D21" t="b">
+        <v>1</v>
+      </c>
+      <c r="F21" t="s">
+        <v>48</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="I21" s="1">
+        <v>0</v>
+      </c>
+      <c r="J21" s="1">
+        <v>0</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="22" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="H22" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="I22">
+        <v>1</v>
+      </c>
+      <c r="J22">
+        <v>1</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="23" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B23" t="s">
+        <v>45</v>
+      </c>
+      <c r="C23" t="b">
+        <v>0</v>
+      </c>
+      <c r="D23" t="b">
+        <v>1</v>
+      </c>
+      <c r="F23" t="s">
+        <v>49</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I23" s="1">
+        <v>0</v>
+      </c>
+      <c r="J23" s="1">
+        <v>0</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="24" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="H24" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="I20">
-        <v>1</v>
-      </c>
-      <c r="J20">
-        <v>1</v>
-      </c>
-      <c r="K20" s="1" t="s">
+      <c r="I24">
+        <v>1</v>
+      </c>
+      <c r="J24">
+        <v>1</v>
+      </c>
+      <c r="K24" s="1" t="s">
         <v>65</v>
       </c>
     </row>

--- a/Tools/Luban/DataTables/Datas/__enums__.xlsx
+++ b/Tools/Luban/DataTables/Datas/__enums__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1_Game_Data\Unity\2025TTGJ\Tools\Luban\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB61493E-058B-4198-9789-60755CD2E9A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2755C22-FD81-406D-AD39-DF7E0AB5F8EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17330" yWindow="6140" windowWidth="18780" windowHeight="12970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38290" yWindow="4430" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="80">
   <si>
     <t>##var</t>
   </si>
@@ -309,6 +309,30 @@
   </si>
   <si>
     <t>seeding</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>if_eat</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>eat_true</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>eat_false</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>吞下有效果</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>吞下无效果</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>吞下有无效果</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -647,7 +671,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L24"/>
+  <dimension ref="A1:L26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
@@ -1113,6 +1137,46 @@
         <v>65</v>
       </c>
     </row>
+    <row r="25" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B25" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C25" t="b">
+        <v>0</v>
+      </c>
+      <c r="D25" t="b">
+        <v>1</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="26" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="H26" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="I26">
+        <v>1</v>
+      </c>
+      <c r="J26">
+        <v>1</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>

--- a/Tools/Luban/DataTables/Datas/__enums__.xlsx
+++ b/Tools/Luban/DataTables/Datas/__enums__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1_Game_Data\Unity\2025TTGJ\Tools\Luban\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2755C22-FD81-406D-AD39-DF7E0AB5F8EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDC4B144-62F5-4F06-B4CB-1AB80B0332BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38290" yWindow="4430" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10430" yWindow="6990" windowWidth="18780" windowHeight="12970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="98">
   <si>
     <t>##var</t>
   </si>
@@ -333,6 +333,78 @@
   </si>
   <si>
     <t>吞下有无效果</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>popcorn_true</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>popcorn_false</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>hidden_door_true</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>hidden_door_false</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ake_true</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ake_false</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>可以被爆米花机吃</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>不可以被爆米花机吃</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>可以被隐藏门吃</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>不可以被隐藏门吃</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>可以被湖神吃</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>不可以被湖神吃</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>if_popcorn</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>是否会被爆米花机吃</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>if_hidden_door</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>是否会被隐藏门吃</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>if_lake</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>是否会被湖神吃</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -671,7 +743,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:L32"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
@@ -1177,6 +1249,139 @@
         <v>77</v>
       </c>
     </row>
+    <row r="27" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B27" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C27" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="D27" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="28" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B28" s="1"/>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+      <c r="H28" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="I28">
+        <v>1</v>
+      </c>
+      <c r="J28">
+        <v>1</v>
+      </c>
+      <c r="K28" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="29" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B29" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C29" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="D29" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="30" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B30" s="1"/>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+      <c r="H30" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="I30">
+        <v>1</v>
+      </c>
+      <c r="J30">
+        <v>1</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="31" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B31" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C31" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="D31" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="32" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="H32" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="I32">
+        <v>1</v>
+      </c>
+      <c r="J32">
+        <v>1</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>

--- a/Tools/Luban/DataTables/Datas/__enums__.xlsx
+++ b/Tools/Luban/DataTables/Datas/__enums__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1_Game_Data\Unity\2025TTGJ\Tools\Luban\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDC4B144-62F5-4F06-B4CB-1AB80B0332BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{120D413B-4AA1-4221-A0F4-551771BB7F6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10430" yWindow="6990" windowWidth="18780" windowHeight="12970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="108">
   <si>
     <t>##var</t>
   </si>
@@ -405,6 +405,45 @@
   </si>
   <si>
     <t>是否会被湖神吃</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>npc</t>
+  </si>
+  <si>
+    <t>NPC枚举</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>甜菜</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>羊</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>猴子</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>绿羊</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>monkey</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>sheep</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>beet</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Green_Sheep</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -743,7 +782,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L32"/>
+  <dimension ref="A1:L36"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
@@ -1382,6 +1421,75 @@
         <v>91</v>
       </c>
     </row>
+    <row r="33" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B33" t="s">
+        <v>98</v>
+      </c>
+      <c r="C33" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="D33" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E33" s="1"/>
+      <c r="F33" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="34" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="H34" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="I34">
+        <v>1</v>
+      </c>
+      <c r="J34">
+        <v>1</v>
+      </c>
+      <c r="K34" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="35" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="H35" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="I35">
+        <v>2</v>
+      </c>
+      <c r="J35">
+        <v>2</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="36" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="H36" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="I36">
+        <v>3</v>
+      </c>
+      <c r="J36">
+        <v>3</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
